--- a/erp-server/erp-server-file/src/main/resources/excel/plm/moldRefSku.xlsx
+++ b/erp-server/erp-server-file/src/main/resources/excel/plm/moldRefSku.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>模具编码</t>
   </si>
@@ -44,6 +44,9 @@
     <t>项目名称</t>
   </si>
   <si>
+    <t>产品经理</t>
+  </si>
+  <si>
     <t>审核状态</t>
   </si>
   <si>
@@ -81,6 +84,9 @@
   </si>
   <si>
     <t>{.projectName}</t>
+  </si>
+  <si>
+    <t>{.chargeName}</t>
   </si>
   <si>
     <t>{.approveStatusName}</t>
@@ -1053,7 +1059,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
@@ -1061,10 +1067,10 @@
     <col min="3" max="3" width="19.25" customWidth="1"/>
     <col min="4" max="4" width="16.75" customWidth="1"/>
     <col min="5" max="5" width="18.625" customWidth="1"/>
-    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="6" max="7" width="19.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1086,13 +1092,13 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -1104,46 +1110,52 @@
       <c r="M1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" t="s">
         <v>18</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M2" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
